--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/20.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/20.xlsx
@@ -426,13 +426,13 @@
         <v>-9.259865778837588</v>
       </c>
       <c r="E2">
-        <v>-22.86640025269285</v>
+        <v>-32.29138187911094</v>
       </c>
       <c r="F2">
-        <v>-3.681524164285587</v>
+        <v>-4.587719169680314</v>
       </c>
       <c r="G2">
-        <v>-13.84017211432995</v>
+        <v>-19.14274242603693</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-9.657490033409561</v>
       </c>
       <c r="E3">
-        <v>-23.34679888932255</v>
+        <v>-32.09846435791017</v>
       </c>
       <c r="F3">
-        <v>-3.74030511518824</v>
+        <v>-4.541076286330883</v>
       </c>
       <c r="G3">
-        <v>-13.81129588086365</v>
+        <v>-19.22133146659369</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.964563755174698</v>
       </c>
       <c r="E4">
-        <v>-22.96247635723958</v>
+        <v>-32.5765149807669</v>
       </c>
       <c r="F4">
-        <v>-3.717404898337847</v>
+        <v>-4.619131689961875</v>
       </c>
       <c r="G4">
-        <v>-13.33163424822419</v>
+        <v>-19.19481399682413</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-10.12859221523426</v>
       </c>
       <c r="E5">
-        <v>-23.7179435620432</v>
+        <v>-33.30148064889185</v>
       </c>
       <c r="F5">
-        <v>-3.535272585851723</v>
+        <v>-4.533250699476636</v>
       </c>
       <c r="G5">
-        <v>-13.55741014345694</v>
+        <v>-19.07977253933445</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-10.14838881726303</v>
       </c>
       <c r="E6">
-        <v>-24.2193588465425</v>
+        <v>-33.13211572100498</v>
       </c>
       <c r="F6">
-        <v>-3.640741980310962</v>
+        <v>-4.637747590604988</v>
       </c>
       <c r="G6">
-        <v>-13.31820998606245</v>
+        <v>-18.87817024762946</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-10.00516388305705</v>
       </c>
       <c r="E7">
-        <v>-24.84797443744325</v>
+        <v>-33.87509339449544</v>
       </c>
       <c r="F7">
-        <v>-3.581590749179258</v>
+        <v>-4.70659486218646</v>
       </c>
       <c r="G7">
-        <v>-13.24111069099836</v>
+        <v>-18.71669507840597</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-9.700373462522551</v>
       </c>
       <c r="E8">
-        <v>-24.26280502617209</v>
+        <v>-33.6676643783371</v>
       </c>
       <c r="F8">
-        <v>-3.444556414836343</v>
+        <v>-4.386776290211419</v>
       </c>
       <c r="G8">
-        <v>-12.89785015566795</v>
+        <v>-18.43176635547751</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-9.223515092925339</v>
       </c>
       <c r="E9">
-        <v>-25.79913058954033</v>
+        <v>-34.59580003281618</v>
       </c>
       <c r="F9">
-        <v>-3.465416362773641</v>
+        <v>-4.447532069002346</v>
       </c>
       <c r="G9">
-        <v>-12.76967245347844</v>
+        <v>-18.38449176517672</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-8.564639936384243</v>
       </c>
       <c r="E10">
-        <v>-25.35429858776687</v>
+        <v>-34.97987123459172</v>
       </c>
       <c r="F10">
-        <v>-3.380854961561062</v>
+        <v>-4.40463423468097</v>
       </c>
       <c r="G10">
-        <v>-12.63616808351625</v>
+        <v>-18.32260442686558</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-7.72775030340221</v>
       </c>
       <c r="E11">
-        <v>-26.23519093716093</v>
+        <v>-35.20642173224746</v>
       </c>
       <c r="F11">
-        <v>-3.259318552957124</v>
+        <v>-4.466755991319114</v>
       </c>
       <c r="G11">
-        <v>-12.0734216894777</v>
+        <v>-17.95318727122939</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.711033269286633</v>
       </c>
       <c r="E12">
-        <v>-26.81128075804671</v>
+        <v>-35.64147449440135</v>
       </c>
       <c r="F12">
-        <v>-3.237664200680542</v>
+        <v>-4.424829831961222</v>
       </c>
       <c r="G12">
-        <v>-12.1285025461601</v>
+        <v>-17.75096094169024</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.50845883258414</v>
       </c>
       <c r="E13">
-        <v>-27.35362439062734</v>
+        <v>-35.91773857971329</v>
       </c>
       <c r="F13">
-        <v>-3.401399301517892</v>
+        <v>-4.435647481874382</v>
       </c>
       <c r="G13">
-        <v>-12.00602560338922</v>
+        <v>-17.41679778550175</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.143235923041196</v>
       </c>
       <c r="E14">
-        <v>-28.26701306950044</v>
+        <v>-36.19152558974303</v>
       </c>
       <c r="F14">
-        <v>-2.998420097608405</v>
+        <v>-4.348305251290604</v>
       </c>
       <c r="G14">
-        <v>-11.28082080810201</v>
+        <v>-17.24275413013841</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-2.638849045417581</v>
       </c>
       <c r="E15">
-        <v>-28.96068471799539</v>
+        <v>-37.10757474709564</v>
       </c>
       <c r="F15">
-        <v>-2.927251740564289</v>
+        <v>-4.057228543090497</v>
       </c>
       <c r="G15">
-        <v>-11.15773472495191</v>
+        <v>-16.72902863917262</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-1.02065309190332</v>
       </c>
       <c r="E16">
-        <v>-28.85683322357748</v>
+        <v>-37.26314141468114</v>
       </c>
       <c r="F16">
-        <v>-2.835259883748598</v>
+        <v>-4.034691151162531</v>
       </c>
       <c r="G16">
-        <v>-11.01044193281866</v>
+        <v>-16.6196697331011</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>0.6532643728252521</v>
       </c>
       <c r="E17">
-        <v>-30.19472558440361</v>
+        <v>-37.98099511437704</v>
       </c>
       <c r="F17">
-        <v>-2.556121606557638</v>
+        <v>-4.114444707969262</v>
       </c>
       <c r="G17">
-        <v>-10.4147423684822</v>
+        <v>-16.66067580542328</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>2.327942969463487</v>
       </c>
       <c r="E18">
-        <v>-30.5044324502622</v>
+        <v>-38.50536976209523</v>
       </c>
       <c r="F18">
-        <v>-2.454238214585118</v>
+        <v>-3.941832822043512</v>
       </c>
       <c r="G18">
-        <v>-10.06706887594794</v>
+        <v>-16.0904624759209</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>3.958408214083303</v>
       </c>
       <c r="E19">
-        <v>-31.24709539480912</v>
+        <v>-39.04002178157383</v>
       </c>
       <c r="F19">
-        <v>-2.316282735690291</v>
+        <v>-3.768531734438633</v>
       </c>
       <c r="G19">
-        <v>-10.12676794365762</v>
+        <v>-16.04631469588196</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>5.482615144510372</v>
       </c>
       <c r="E20">
-        <v>-31.71017714683349</v>
+        <v>-40.02863067795134</v>
       </c>
       <c r="F20">
-        <v>-2.042412875181135</v>
+        <v>-3.640735353371739</v>
       </c>
       <c r="G20">
-        <v>-9.840544797423309</v>
+        <v>-15.83315528969936</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>6.852857888709385</v>
       </c>
       <c r="E21">
-        <v>-33.2132478613264</v>
+        <v>-39.8069188547728</v>
       </c>
       <c r="F21">
-        <v>-2.048082221685895</v>
+        <v>-3.588261591874002</v>
       </c>
       <c r="G21">
-        <v>-9.903580895036571</v>
+        <v>-15.66476273557156</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>8.042792265956228</v>
       </c>
       <c r="E22">
-        <v>-33.22413431284085</v>
+        <v>-40.72149852230993</v>
       </c>
       <c r="F22">
-        <v>-1.808967343928595</v>
+        <v>-3.294260746742013</v>
       </c>
       <c r="G22">
-        <v>-9.916389395728013</v>
+        <v>-15.55802247102161</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>9.021141643858371</v>
       </c>
       <c r="E23">
-        <v>-33.59041540447726</v>
+        <v>-41.26978351278861</v>
       </c>
       <c r="F23">
-        <v>-1.617572227144367</v>
+        <v>-3.370964254771636</v>
       </c>
       <c r="G23">
-        <v>-9.765670188961613</v>
+        <v>-15.37908913989678</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>9.771672118061094</v>
       </c>
       <c r="E24">
-        <v>-33.80392163275389</v>
+        <v>-41.13092238581741</v>
       </c>
       <c r="F24">
-        <v>-1.715452119459156</v>
+        <v>-3.098389960880458</v>
       </c>
       <c r="G24">
-        <v>-9.850688308955636</v>
+        <v>-15.4507293453666</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>10.29808949091812</v>
       </c>
       <c r="E25">
-        <v>-34.35845818160017</v>
+        <v>-41.20919705903999</v>
       </c>
       <c r="F25">
-        <v>-1.455219671502289</v>
+        <v>-3.070550189207172</v>
       </c>
       <c r="G25">
-        <v>-9.499525501422983</v>
+        <v>-15.68831561181071</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>10.60316830345869</v>
       </c>
       <c r="E26">
-        <v>-34.89843115803778</v>
+        <v>-41.29907368267023</v>
       </c>
       <c r="F26">
-        <v>-1.575786890244951</v>
+        <v>-3.091965143304345</v>
       </c>
       <c r="G26">
-        <v>-9.593061655089553</v>
+        <v>-15.66000548163163</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>10.69783652633786</v>
       </c>
       <c r="E27">
-        <v>-34.31967180172447</v>
+        <v>-41.5732954262047</v>
       </c>
       <c r="F27">
-        <v>-1.436009003063966</v>
+        <v>-3.104760106207987</v>
       </c>
       <c r="G27">
-        <v>-9.563945407071662</v>
+        <v>-15.60292340017075</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>10.60387087985379</v>
       </c>
       <c r="E28">
-        <v>-34.53195760625604</v>
+        <v>-41.51694535989026</v>
       </c>
       <c r="F28">
-        <v>-1.308603611411193</v>
+        <v>-2.984517607487221</v>
       </c>
       <c r="G28">
-        <v>-9.630159628402625</v>
+        <v>-16.02328654111079</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>10.34373091685833</v>
       </c>
       <c r="E29">
-        <v>-34.37217040089539</v>
+        <v>-41.47591512114376</v>
       </c>
       <c r="F29">
-        <v>-1.288609307409821</v>
+        <v>-3.126429369097818</v>
       </c>
       <c r="G29">
-        <v>-9.889180021940742</v>
+        <v>-15.69572957854591</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>9.940698623351755</v>
       </c>
       <c r="E30">
-        <v>-34.15428740249034</v>
+        <v>-41.44170702848982</v>
       </c>
       <c r="F30">
-        <v>-1.173825749873505</v>
+        <v>-2.895368707597938</v>
       </c>
       <c r="G30">
-        <v>-9.923017107897634</v>
+        <v>-15.48517060588441</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>9.419834059967492</v>
       </c>
       <c r="E31">
-        <v>-33.58656167309672</v>
+        <v>-41.31953332823688</v>
       </c>
       <c r="F31">
-        <v>-1.281336241613242</v>
+        <v>-2.978601407496427</v>
       </c>
       <c r="G31">
-        <v>-9.751232899864851</v>
+        <v>-15.78842319837273</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>8.809123255640891</v>
       </c>
       <c r="E32">
-        <v>-33.37686162722353</v>
+        <v>-40.94153707434263</v>
       </c>
       <c r="F32">
-        <v>-1.461597272136442</v>
+        <v>-3.059517992136688</v>
       </c>
       <c r="G32">
-        <v>-10.10851359555408</v>
+        <v>-16.07800489305663</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>8.133474822418949</v>
       </c>
       <c r="E33">
-        <v>-33.43041536083825</v>
+        <v>-40.784120525125</v>
       </c>
       <c r="F33">
-        <v>-1.466762142892897</v>
+        <v>-3.136754140406312</v>
       </c>
       <c r="G33">
-        <v>-9.74147010106954</v>
+        <v>-15.84792032280451</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>7.412841986561738</v>
       </c>
       <c r="E34">
-        <v>-33.00114545999214</v>
+        <v>-40.11991339276096</v>
       </c>
       <c r="F34">
-        <v>-1.3305611461572</v>
+        <v>-2.904991851716261</v>
       </c>
       <c r="G34">
-        <v>-10.79161487267283</v>
+        <v>-16.07537300935291</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>6.670389200239582</v>
       </c>
       <c r="E35">
-        <v>-31.98890698624261</v>
+        <v>-40.25065949431042</v>
       </c>
       <c r="F35">
-        <v>-1.513111784181738</v>
+        <v>-3.028562730661474</v>
       </c>
       <c r="G35">
-        <v>-10.46049741838047</v>
+        <v>-16.55641182893671</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>5.924742995919389</v>
       </c>
       <c r="E36">
-        <v>-32.5515381823776</v>
+        <v>-39.94623282914478</v>
       </c>
       <c r="F36">
-        <v>-1.346331604771697</v>
+        <v>-3.06529419803641</v>
       </c>
       <c r="G36">
-        <v>-10.3010218186627</v>
+        <v>-16.36653383425904</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>5.182645394981593</v>
       </c>
       <c r="E37">
-        <v>-31.70026658146771</v>
+        <v>-39.62282053670198</v>
       </c>
       <c r="F37">
-        <v>-1.381924895335186</v>
+        <v>-2.897255728541516</v>
       </c>
       <c r="G37">
-        <v>-9.969205839261544</v>
+        <v>-15.98877741440942</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>4.454978874244882</v>
       </c>
       <c r="E38">
-        <v>-31.23335600466985</v>
+        <v>-39.01965496972434</v>
       </c>
       <c r="F38">
-        <v>-1.266986433094546</v>
+        <v>-3.084576106071374</v>
       </c>
       <c r="G38">
-        <v>-10.39969593900621</v>
+        <v>-16.45762349477209</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>3.750868768840785</v>
       </c>
       <c r="E39">
-        <v>-31.02223401795825</v>
+        <v>-38.4414073309739</v>
       </c>
       <c r="F39">
-        <v>-1.268355724411374</v>
+        <v>-2.871064407999801</v>
       </c>
       <c r="G39">
-        <v>-10.50689802465889</v>
+        <v>-16.56864263943154</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>3.066362793338715</v>
       </c>
       <c r="E40">
-        <v>-30.71118219531939</v>
+        <v>-38.34167901213997</v>
       </c>
       <c r="F40">
-        <v>-1.418697781080261</v>
+        <v>-3.01745349542253</v>
       </c>
       <c r="G40">
-        <v>-10.57982934288904</v>
+        <v>-16.27541437883614</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>2.401902817785358</v>
       </c>
       <c r="E41">
-        <v>-30.30988014994466</v>
+        <v>-37.66397249875907</v>
       </c>
       <c r="F41">
-        <v>-1.17556697815419</v>
+        <v>-2.777258426571979</v>
       </c>
       <c r="G41">
-        <v>-10.42569365312611</v>
+        <v>-16.52533739323234</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>1.760723675286429</v>
       </c>
       <c r="E42">
-        <v>-29.32255507594833</v>
+        <v>-37.29584152549052</v>
       </c>
       <c r="F42">
-        <v>-1.218363751652423</v>
+        <v>-2.822374628798052</v>
       </c>
       <c r="G42">
-        <v>-10.59696803714584</v>
+        <v>-16.39927844018797</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>1.132646743126092</v>
       </c>
       <c r="E43">
-        <v>-28.56963287353702</v>
+        <v>-36.9069950478739</v>
       </c>
       <c r="F43">
-        <v>-1.090349509958593</v>
+        <v>-2.779401413043022</v>
       </c>
       <c r="G43">
-        <v>-10.71308211139024</v>
+        <v>-16.65771121189287</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>0.5132419911997421</v>
       </c>
       <c r="E44">
-        <v>-28.27120190795754</v>
+        <v>-36.4457269496896</v>
       </c>
       <c r="F44">
-        <v>-1.169531493257393</v>
+        <v>-2.676580309170533</v>
       </c>
       <c r="G44">
-        <v>-10.77061608231723</v>
+        <v>-16.37631980687313</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-0.09486716298078718</v>
       </c>
       <c r="E45">
-        <v>-27.4962396225509</v>
+        <v>-35.87885710188343</v>
       </c>
       <c r="F45">
-        <v>-1.338096804420467</v>
+        <v>-2.800639924883398</v>
       </c>
       <c r="G45">
-        <v>-10.46238111879231</v>
+        <v>-16.52817453075949</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.7011294615588722</v>
       </c>
       <c r="E46">
-        <v>-27.33283416645812</v>
+        <v>-35.93870994284281</v>
       </c>
       <c r="F46">
-        <v>-1.084516146708079</v>
+        <v>-2.677696948429507</v>
       </c>
       <c r="G46">
-        <v>-11.17112257111272</v>
+        <v>-16.72896242826183</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.309145931453424</v>
       </c>
       <c r="E47">
-        <v>-26.91284537309074</v>
+        <v>-35.25608777092658</v>
       </c>
       <c r="F47">
-        <v>-1.245164750602599</v>
+        <v>-2.77963749775282</v>
       </c>
       <c r="G47">
-        <v>-10.52285154361264</v>
+        <v>-16.68784876320962</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.912045718840739</v>
       </c>
       <c r="E48">
-        <v>-26.45618499720925</v>
+        <v>-34.66869714315465</v>
       </c>
       <c r="F48">
-        <v>-1.130952766574214</v>
+        <v>-2.766169900518105</v>
       </c>
       <c r="G48">
-        <v>-10.55762882450268</v>
+        <v>-16.75129205792421</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-2.512447940345374</v>
       </c>
       <c r="E49">
-        <v>-26.19616001968882</v>
+        <v>-34.66535060086299</v>
       </c>
       <c r="F49">
-        <v>-1.05336124868879</v>
+        <v>-2.673391094669755</v>
       </c>
       <c r="G49">
-        <v>-10.64068710153746</v>
+        <v>-16.68639212317234</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.108180535113238</v>
       </c>
       <c r="E50">
-        <v>-25.46293215073687</v>
+        <v>-34.43869141983107</v>
       </c>
       <c r="F50">
-        <v>-0.9345377433290204</v>
+        <v>-2.593256488857736</v>
       </c>
       <c r="G50">
-        <v>-10.55295764474677</v>
+        <v>-16.57913541351827</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.686453651420751</v>
       </c>
       <c r="E51">
-        <v>-24.96964547708134</v>
+        <v>-33.32367017152944</v>
       </c>
       <c r="F51">
-        <v>-0.8716041866361336</v>
+        <v>-2.742463682184789</v>
       </c>
       <c r="G51">
-        <v>-10.89962473143709</v>
+        <v>-16.63952804051842</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.242718685329814</v>
       </c>
       <c r="E52">
-        <v>-24.31615950693046</v>
+        <v>-33.56243849205786</v>
       </c>
       <c r="F52">
-        <v>-1.24475388037081</v>
+        <v>-2.677890786401762</v>
       </c>
       <c r="G52">
-        <v>-10.48600517176055</v>
+        <v>-17.11605293125942</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.770682866377851</v>
       </c>
       <c r="E53">
-        <v>-23.48430147409145</v>
+        <v>-33.03943823620101</v>
       </c>
       <c r="F53">
-        <v>-0.9853000977725741</v>
+        <v>-2.590569265003055</v>
       </c>
       <c r="G53">
-        <v>-10.90983776442575</v>
+        <v>-17.0321852258403</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-5.256483278089856</v>
       </c>
       <c r="E54">
-        <v>-23.56863977401031</v>
+        <v>-32.52742632252376</v>
       </c>
       <c r="F54">
-        <v>-1.038720683211712</v>
+        <v>-2.623068603317088</v>
       </c>
       <c r="G54">
-        <v>-10.67790094394441</v>
+        <v>-16.81385640279813</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-5.694869518330314</v>
       </c>
       <c r="E55">
-        <v>-23.28272098211401</v>
+        <v>-32.45805462920026</v>
       </c>
       <c r="F55">
-        <v>-1.205787477743121</v>
+        <v>-2.690159736004625</v>
       </c>
       <c r="G55">
-        <v>-11.05509457105235</v>
+        <v>-16.96660000816179</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-6.082037034343157</v>
       </c>
       <c r="E56">
-        <v>-22.83793426508063</v>
+        <v>-32.40387823040949</v>
       </c>
       <c r="F56">
-        <v>-1.069916999601141</v>
+        <v>-2.565320626565726</v>
       </c>
       <c r="G56">
-        <v>-11.1012866129618</v>
+        <v>-16.9130618657007</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-6.410442918452529</v>
       </c>
       <c r="E57">
-        <v>-21.64168804274042</v>
+        <v>-31.82385316561104</v>
       </c>
       <c r="F57">
-        <v>-0.8702481491977507</v>
+        <v>-2.663178981328043</v>
       </c>
       <c r="G57">
-        <v>-11.0000600620075</v>
+        <v>-16.88942622582308</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-6.678506766236564</v>
       </c>
       <c r="E58">
-        <v>-21.70481044193334</v>
+        <v>-31.11441110638438</v>
       </c>
       <c r="F58">
-        <v>-1.023680844646484</v>
+        <v>-2.688406082212899</v>
       </c>
       <c r="G58">
-        <v>-10.69396371090095</v>
+        <v>-17.22222212670385</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.887369416388328</v>
       </c>
       <c r="E59">
-        <v>-21.64596745067767</v>
+        <v>-31.14770218305177</v>
       </c>
       <c r="F59">
-        <v>-1.204962423809933</v>
+        <v>-2.653839967228881</v>
       </c>
       <c r="G59">
-        <v>-11.11755463374178</v>
+        <v>-17.10865220670638</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.037221652729374</v>
       </c>
       <c r="E60">
-        <v>-21.47437904205303</v>
+        <v>-30.78839041291317</v>
       </c>
       <c r="F60">
-        <v>-1.1790320390001</v>
+        <v>-2.697433630168608</v>
       </c>
       <c r="G60">
-        <v>-11.3721918649859</v>
+        <v>-17.21826105896611</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.130221293631998</v>
       </c>
       <c r="E61">
-        <v>-21.38695685133496</v>
+        <v>-30.85968444345292</v>
       </c>
       <c r="F61">
-        <v>-1.287244157930008</v>
+        <v>-2.656768245997777</v>
       </c>
       <c r="G61">
-        <v>-11.14778984615194</v>
+        <v>-17.16167555933612</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.16933948366924</v>
       </c>
       <c r="E62">
-        <v>-20.30097444260752</v>
+        <v>-30.7814437337854</v>
       </c>
       <c r="F62">
-        <v>-1.262645787903877</v>
+        <v>-2.781401920320782</v>
       </c>
       <c r="G62">
-        <v>-11.13852031864198</v>
+        <v>-17.2342178884654</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.158312209622584</v>
       </c>
       <c r="E63">
-        <v>-20.79747180433449</v>
+        <v>-30.42839031472539</v>
       </c>
       <c r="F63">
-        <v>-1.263565275720984</v>
+        <v>-2.826709475416902</v>
       </c>
       <c r="G63">
-        <v>-11.39092955273817</v>
+        <v>-17.17142511594927</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.097982084692614</v>
       </c>
       <c r="E64">
-        <v>-20.54985031712106</v>
+        <v>-30.14022087124729</v>
       </c>
       <c r="F64">
-        <v>-1.469249730203504</v>
+        <v>-2.681222480095822</v>
       </c>
       <c r="G64">
-        <v>-10.97205615729081</v>
+        <v>-17.30268328076307</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.986954846120859</v>
       </c>
       <c r="E65">
-        <v>-20.18906679292996</v>
+        <v>-30.11895968578128</v>
       </c>
       <c r="F65">
-        <v>-1.571536537101187</v>
+        <v>-2.850951647459829</v>
       </c>
       <c r="G65">
-        <v>-11.36878200308045</v>
+        <v>-17.38187484060797</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-6.827053297848233</v>
       </c>
       <c r="E66">
-        <v>-19.58010930769651</v>
+        <v>-30.26164737328897</v>
       </c>
       <c r="F66">
-        <v>-1.455247007626581</v>
+        <v>-3.005348562565421</v>
       </c>
       <c r="G66">
-        <v>-11.24295147767829</v>
+        <v>-17.48825756623969</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-6.614531139173967</v>
       </c>
       <c r="E67">
-        <v>-20.31717732260696</v>
+        <v>-30.22377121668881</v>
       </c>
       <c r="F67">
-        <v>-1.823401645922377</v>
+        <v>-3.137811965579687</v>
       </c>
       <c r="G67">
-        <v>-11.52617858019956</v>
+        <v>-17.43172338006555</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-6.343163192948778</v>
       </c>
       <c r="E68">
-        <v>-20.48819967198064</v>
+        <v>-30.1643757516042</v>
       </c>
       <c r="F68">
-        <v>-1.585704104791267</v>
+        <v>-3.218219932634629</v>
       </c>
       <c r="G68">
-        <v>-11.36437897751322</v>
+        <v>-16.93346806840477</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-6.014824144333664</v>
       </c>
       <c r="E69">
-        <v>-19.40161497621018</v>
+        <v>-29.96325716397555</v>
       </c>
       <c r="F69">
-        <v>-1.793878631686602</v>
+        <v>-3.19327613340153</v>
       </c>
       <c r="G69">
-        <v>-11.02466072590983</v>
+        <v>-17.31499188907808</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.627340752127604</v>
       </c>
       <c r="E70">
-        <v>-19.72901459001672</v>
+        <v>-29.92076875659858</v>
       </c>
       <c r="F70">
-        <v>-1.901047836056386</v>
+        <v>-3.295002963934921</v>
       </c>
       <c r="G70">
-        <v>-11.08458491071618</v>
+        <v>-16.85748608246019</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.176311566766818</v>
       </c>
       <c r="E71">
-        <v>-19.59638464328008</v>
+        <v>-29.87737918289409</v>
       </c>
       <c r="F71">
-        <v>-2.011296082062374</v>
+        <v>-3.350844867292441</v>
       </c>
       <c r="G71">
-        <v>-11.03646613130287</v>
+        <v>-16.90220162105912</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.668147251819332</v>
       </c>
       <c r="E72">
-        <v>-20.29603840593915</v>
+        <v>-29.73258122649883</v>
       </c>
       <c r="F72">
-        <v>-2.288242499105528</v>
+        <v>-3.36964300876417</v>
       </c>
       <c r="G72">
-        <v>-10.87144867835236</v>
+        <v>-17.01067164565334</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.106456020204279</v>
       </c>
       <c r="E73">
-        <v>-19.58370944453261</v>
+        <v>-29.63189739964929</v>
       </c>
       <c r="F73">
-        <v>-2.045163054958429</v>
+        <v>-3.577547487886193</v>
       </c>
       <c r="G73">
-        <v>-10.73841771640228</v>
+        <v>-17.14771167825148</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.49232828749729</v>
       </c>
       <c r="E74">
-        <v>-20.3067527754413</v>
+        <v>-29.94205711290864</v>
       </c>
       <c r="F74">
-        <v>-2.253145400616316</v>
+        <v>-3.535912085486684</v>
       </c>
       <c r="G74">
-        <v>-10.26654910796226</v>
+        <v>-16.69100536838132</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-2.839234907121605</v>
       </c>
       <c r="E75">
-        <v>-20.02816105448942</v>
+        <v>-30.49987227693647</v>
       </c>
       <c r="F75">
-        <v>-2.308926004786028</v>
+        <v>-3.53190444399194</v>
       </c>
       <c r="G75">
-        <v>-10.45561767425558</v>
+        <v>-16.59353794188686</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-2.159724234194235</v>
       </c>
       <c r="E76">
-        <v>-20.72181458908834</v>
+        <v>-29.64788970560738</v>
       </c>
       <c r="F76">
-        <v>-2.567187766691636</v>
+        <v>-3.794077756773567</v>
       </c>
       <c r="G76">
-        <v>-10.26367886497972</v>
+        <v>-16.63107621775666</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-1.462395709655025</v>
       </c>
       <c r="E77">
-        <v>-21.19434273789271</v>
+        <v>-30.27103263566986</v>
       </c>
       <c r="F77">
-        <v>-2.647196460658429</v>
+        <v>-3.884477491441077</v>
       </c>
       <c r="G77">
-        <v>-10.4031091114572</v>
+        <v>-16.39538854917933</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-0.7672331881810445</v>
       </c>
       <c r="E78">
-        <v>-21.08922779922666</v>
+        <v>-30.7621954550158</v>
       </c>
       <c r="F78">
-        <v>-2.718648947721706</v>
+        <v>-3.787611520827314</v>
       </c>
       <c r="G78">
-        <v>-10.07915567771182</v>
+        <v>-16.21526507693312</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-0.09266999892415614</v>
       </c>
       <c r="E79">
-        <v>-20.87495852307973</v>
+        <v>-30.6415795498215</v>
       </c>
       <c r="F79">
-        <v>-2.667283541808914</v>
+        <v>-4.023879299821192</v>
       </c>
       <c r="G79">
-        <v>-10.43337080823168</v>
+        <v>-16.3054046108764</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>0.5496418824209404</v>
       </c>
       <c r="E80">
-        <v>-21.82732377773685</v>
+        <v>-30.80261434977126</v>
       </c>
       <c r="F80">
-        <v>-2.738409652115488</v>
+        <v>-3.985545769889242</v>
       </c>
       <c r="G80">
-        <v>-9.779349363129882</v>
+        <v>-16.23247329264625</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>1.140967433223002</v>
       </c>
       <c r="E81">
-        <v>-22.13181837001261</v>
+        <v>-31.48397307743935</v>
       </c>
       <c r="F81">
-        <v>-2.755165867939317</v>
+        <v>-4.099549833699524</v>
       </c>
       <c r="G81">
-        <v>-9.569795141039554</v>
+        <v>-15.74763727732891</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>1.665529021989791</v>
       </c>
       <c r="E82">
-        <v>-22.51475971752324</v>
+        <v>-31.60567355215849</v>
       </c>
       <c r="F82">
-        <v>-2.474601142080735</v>
+        <v>-3.988712618470144</v>
       </c>
       <c r="G82">
-        <v>-9.495327729679188</v>
+        <v>-16.22525961391618</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>2.11541585194723</v>
       </c>
       <c r="E83">
-        <v>-23.09444061829711</v>
+        <v>-32.10200336034717</v>
       </c>
       <c r="F83">
-        <v>-2.777815089466661</v>
+        <v>-4.116101442774861</v>
       </c>
       <c r="G83">
-        <v>-9.10412718439459</v>
+        <v>-16.02031036067098</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>2.47926827347871</v>
       </c>
       <c r="E84">
-        <v>-24.01786439557121</v>
+        <v>-32.82034839947291</v>
       </c>
       <c r="F84">
-        <v>-3.09865669518416</v>
+        <v>-4.043683079319919</v>
       </c>
       <c r="G84">
-        <v>-9.247391042606552</v>
+        <v>-16.06649578148935</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>2.748824232858879</v>
       </c>
       <c r="E85">
-        <v>-24.74745589989499</v>
+        <v>-33.6048476511397</v>
       </c>
       <c r="F85">
-        <v>-2.940503133906872</v>
+        <v>-4.083265787295291</v>
       </c>
       <c r="G85">
-        <v>-9.00428775202125</v>
+        <v>-15.85235479855437</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>2.920690672347819</v>
       </c>
       <c r="E86">
-        <v>-25.63086155236331</v>
+        <v>-34.05642255071058</v>
       </c>
       <c r="F86">
-        <v>-2.992839386415745</v>
+        <v>-4.232668475329405</v>
       </c>
       <c r="G86">
-        <v>-9.02341608414716</v>
+        <v>-15.97525549115427</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>2.990229641846019</v>
       </c>
       <c r="E87">
-        <v>-26.82975693199801</v>
+        <v>-34.7733411205239</v>
       </c>
       <c r="F87">
-        <v>-3.096495484630256</v>
+        <v>-4.348621687638474</v>
       </c>
       <c r="G87">
-        <v>-9.023733896518928</v>
+        <v>-15.83041746853839</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>2.956471329871607</v>
       </c>
       <c r="E88">
-        <v>-27.60633135415138</v>
+        <v>-35.15402955221571</v>
       </c>
       <c r="F88">
-        <v>-2.982121140590922</v>
+        <v>-4.247604767969282</v>
       </c>
       <c r="G88">
-        <v>-8.761700906540076</v>
+        <v>-15.79393360142285</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>2.819816997751874</v>
       </c>
       <c r="E89">
-        <v>-28.76194810769476</v>
+        <v>-36.23984440740487</v>
       </c>
       <c r="F89">
-        <v>-2.964925061676207</v>
+        <v>-4.36965310762815</v>
       </c>
       <c r="G89">
-        <v>-8.466837236448269</v>
+        <v>-15.75713357720831</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>2.581739322308081</v>
       </c>
       <c r="E90">
-        <v>-30.04704751853948</v>
+        <v>-37.43866506721844</v>
       </c>
       <c r="F90">
-        <v>-2.890842508109042</v>
+        <v>-4.515328142349666</v>
       </c>
       <c r="G90">
-        <v>-8.982822174744616</v>
+        <v>-15.93643272361524</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>2.249671222071724</v>
       </c>
       <c r="E91">
-        <v>-31.41558632721251</v>
+        <v>-38.20981437751062</v>
       </c>
       <c r="F91">
-        <v>-3.264939854152521</v>
+        <v>-4.299798541284874</v>
       </c>
       <c r="G91">
-        <v>-9.154864605329461</v>
+        <v>-15.57299441322297</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>1.828974288772552</v>
       </c>
       <c r="E92">
-        <v>-32.86355004150609</v>
+        <v>-39.40763424456849</v>
       </c>
       <c r="F92">
-        <v>-3.359605680944449</v>
+        <v>-4.673238991977932</v>
       </c>
       <c r="G92">
-        <v>-8.761475789443406</v>
+        <v>-15.93547763122716</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>1.328766766742609</v>
       </c>
       <c r="E93">
-        <v>-33.66722511635835</v>
+        <v>-40.24178142101838</v>
       </c>
       <c r="F93">
-        <v>-3.431345611496497</v>
+        <v>-4.724334350117412</v>
       </c>
       <c r="G93">
-        <v>-9.299747320310125</v>
+        <v>-16.27602351921536</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>0.7655867057607356</v>
       </c>
       <c r="E94">
-        <v>-35.53389833011214</v>
+        <v>-41.25781022751234</v>
       </c>
       <c r="F94">
-        <v>-3.389489035000441</v>
+        <v>-4.7423215199018</v>
       </c>
       <c r="G94">
-        <v>-9.311340850788653</v>
+        <v>-16.1799630745751</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>0.1525628568413914</v>
       </c>
       <c r="E95">
-        <v>-37.12162886617845</v>
+        <v>-42.48016989521778</v>
       </c>
       <c r="F95">
-        <v>-3.486538074810222</v>
+        <v>-4.740195929146217</v>
       </c>
       <c r="G95">
-        <v>-9.704216532116122</v>
+        <v>-15.97087398413304</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-0.4976694296778559</v>
       </c>
       <c r="E96">
-        <v>-38.76980320906213</v>
+        <v>-44.31323503912363</v>
       </c>
       <c r="F96">
-        <v>-3.632425171586855</v>
+        <v>-4.981920164222335</v>
       </c>
       <c r="G96">
-        <v>-9.589463092088364</v>
+        <v>-16.13803004950192</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-1.156185837040347</v>
       </c>
       <c r="E97">
-        <v>-40.75096077420383</v>
+        <v>-45.51011977629892</v>
       </c>
       <c r="F97">
-        <v>-3.518162657146899</v>
+        <v>-5.101569551882696</v>
       </c>
       <c r="G97">
-        <v>-10.32194777701643</v>
+        <v>-16.87929761174567</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-1.821930170439518</v>
       </c>
       <c r="E98">
-        <v>-42.39177861106206</v>
+        <v>-46.67696035267033</v>
       </c>
       <c r="F98">
-        <v>-3.6576489590021</v>
+        <v>-4.970210362616361</v>
       </c>
       <c r="G98">
-        <v>-10.22412115633096</v>
+        <v>-16.62061654912533</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.463916363548104</v>
       </c>
       <c r="E99">
-        <v>-44.45028930496578</v>
+        <v>-48.39317275328226</v>
       </c>
       <c r="F99">
-        <v>-3.722426461533618</v>
+        <v>-5.237580852483152</v>
       </c>
       <c r="G99">
-        <v>-10.38417941206365</v>
+        <v>-17.07728809826733</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.097514428213663</v>
       </c>
       <c r="E100">
-        <v>-45.80283127920672</v>
+        <v>-49.71323877617719</v>
       </c>
       <c r="F100">
-        <v>-3.867582109893578</v>
+        <v>-5.301705601501264</v>
       </c>
       <c r="G100">
-        <v>-10.79658069098174</v>
+        <v>-17.51925751466942</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.67341844040568</v>
       </c>
       <c r="E101">
-        <v>-48.2563494396145</v>
+        <v>-51.30553854251724</v>
       </c>
       <c r="F101">
-        <v>-3.993441767972727</v>
+        <v>-5.374514954370327</v>
       </c>
       <c r="G101">
-        <v>-11.34447597773112</v>
+        <v>-17.57259536912539</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.271151241703397</v>
       </c>
       <c r="E102">
-        <v>-50.17316418181822</v>
+        <v>-53.37420999997567</v>
       </c>
       <c r="F102">
-        <v>-4.025144216845266</v>
+        <v>-5.428260259831362</v>
       </c>
       <c r="G102">
-        <v>-11.4710248915153</v>
+        <v>-17.45058190273001</v>
       </c>
     </row>
   </sheetData>
